--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>545.75</v>
+        <v>538.7</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>354.63</v>
+        <v>350.05</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>518.47</v>
+        <v>511.77</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>155.54</v>
+        <v>153.53</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>22826.07</v>
+        <v>22531.03</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>271.96</v>
+        <v>268.44</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15222.39</v>
+        <v>15025.63</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23715.7</v>
+        <v>23409.16</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1964.72</v>
+        <v>1939.32</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>130.65</v>
+        <v>128.96</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10678.56</v>
+        <v>10540.53</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>671.9299999999999</v>
+        <v>663.25</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4802.64</v>
+        <v>4740.56</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2401.32</v>
+        <v>2370.28</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>768.42</v>
+        <v>758.49</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>35099.37</v>
+        <v>34645.69</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12189.1</v>
+        <v>12031.55</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8994.93</v>
+        <v>8880.68</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>160.65</v>
+        <v>158.61</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>311.08</v>
+        <v>307.13</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>24549.71</v>
+        <v>24237.87</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>18875.79</v>
+        <v>18636.03</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>248.83</v>
+        <v>245.67</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5061.91</v>
+        <v>4997.62</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37111.31</v>
+        <v>36639.92</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7209.28</v>
+        <v>7117.71</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>30848.77</v>
+        <v>30456.92</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>829.55</v>
+        <v>819.01</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>951.5700000000001</v>
+        <v>939.48</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>642.62</v>
+        <v>634.46</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>729.13</v>
+        <v>719.86</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3104.74</v>
+        <v>3065.3</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>553.22</v>
+        <v>546.1900000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>296.59</v>
+        <v>292.83</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15655.1</v>
+        <v>15456.25</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2613.07</v>
+        <v>2579.88</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16718.55</v>
+        <v>16506.19</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>134801.34</v>
+        <v>133460.13</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>87320.71000000001</v>
+        <v>86451.91</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1391.8</v>
+        <v>1377.96</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>222.94</v>
+        <v>220.72</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4898.69</v>
+        <v>4849.95</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10789.29</v>
+        <v>10681.94</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>665.63</v>
+        <v>659.01</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>37.33</v>
+        <v>36.96</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>31108</v>
+        <v>30798.49</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>115.26</v>
+        <v>114.12</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>58483.04</v>
+        <v>57901.16</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3798.45</v>
+        <v>3760.66</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>192.11</v>
+        <v>190.19</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4742.61</v>
+        <v>4695.42</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2420.53</v>
+        <v>2396.45</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1267.9</v>
+        <v>1255.28</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6219.01</v>
+        <v>6157.13</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>37307.77</v>
+        <v>36936.58</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5602.07</v>
+        <v>5546.33</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>444.89</v>
+        <v>440.46</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>873.62</v>
+        <v>864.92</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3831.42</v>
+        <v>3793.3</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1294.41</v>
+        <v>1281.54</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1500.96</v>
+        <v>1486.03</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>18067.53</v>
+        <v>17887.76</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>26109.44</v>
+        <v>25849.66</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2226.3</v>
+        <v>2204.15</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>124.43</v>
+        <v>123.19</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>8451.809999999999</v>
+        <v>8367.719999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2167.53</v>
+        <v>2145.97</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8020.68</v>
+        <v>7940.88</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>247.16</v>
+        <v>244.7</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1445.89</v>
+        <v>1431.51</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>39.73</v>
+        <v>39.34</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>160.65</v>
+        <v>159.06</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>123.58</v>
+        <v>122.35</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>719.63</v>
+        <v>712.47</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>15927.3</v>
+        <v>15768.83</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4832.15</v>
+        <v>4814.82</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>46890.13</v>
+        <v>46721.99</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>13098.11</v>
+        <v>13051.14</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>16372.63</v>
+        <v>16313.92</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>14392.63</v>
+        <v>14341.03</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>12550</v>
+        <v>12505</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>24231.5</v>
+        <v>24144.61</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>201.93</v>
+        <v>201.2</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>628.23</v>
+        <v>625.98</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>605.13</v>
+        <v>602.96</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>10563.17</v>
+        <v>10525.29</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2921.87</v>
+        <v>2911.39</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>365.66</v>
+        <v>364.34</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>17627.87</v>
+        <v>17564.66</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>267.42</v>
+        <v>266.46</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>764.0599999999999</v>
+        <v>761.3200000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1702.75</v>
+        <v>1696.65</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>873.21</v>
+        <v>870.08</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8248.809999999999</v>
+        <v>8219.23</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>523.92</v>
+        <v>522.05</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>5457.54</v>
+        <v>5437.97</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>39893.94</v>
+        <v>39750.89</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1375.3</v>
+        <v>1370.37</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>218.3</v>
+        <v>217.52</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>12552.35</v>
+        <v>12507.34</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>12798.71</v>
+        <v>12752.82</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15032.82</v>
+        <v>14978.91</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>234.8</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>60660.6</v>
+        <v>60529.33</v>
       </c>
     </row>
     <row r="106">
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1285123.72</v>
+        <v>1282342.54</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>216118.75</v>
+        <v>215651.04</v>
       </c>
     </row>
     <row r="108">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>35644.31</v>
+        <v>35567.17</v>
       </c>
     </row>
     <row r="109">
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>15877.52</v>
+        <v>15843.16</v>
       </c>
     </row>
     <row r="110">
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>21859.65</v>
+        <v>21812.34</v>
       </c>
     </row>
     <row r="111">
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1688.13</v>
+        <v>1684.47</v>
       </c>
     </row>
     <row r="112">
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>163.73</v>
+        <v>163.37</v>
       </c>
     </row>
     <row r="113">
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1375.48</v>
+        <v>1372.5</v>
       </c>
     </row>
     <row r="114">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5457.54</v>
+        <v>5445.73</v>
       </c>
     </row>
     <row r="115">
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>30024.9</v>
+        <v>29959.92</v>
       </c>
     </row>
     <row r="116">
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>51.85</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="117">
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9638.360000000001</v>
+        <v>9617.5</v>
       </c>
     </row>
     <row r="118">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>36292.67</v>
+        <v>36214.13</v>
       </c>
     </row>
     <row r="119">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>38880.85</v>
+        <v>38796.71</v>
       </c>
     </row>
     <row r="120">
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>57015.78</v>
+        <v>56892.39</v>
       </c>
     </row>
     <row r="121">
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>507.55</v>
+        <v>506.45</v>
       </c>
     </row>
     <row r="122">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>12699.7</v>
+        <v>12672.22</v>
       </c>
     </row>
     <row r="123">
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>987.16</v>
+        <v>985.02</v>
       </c>
     </row>
     <row r="124">
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>6112.45</v>
+        <v>6099.22</v>
       </c>
     </row>
     <row r="125">
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>44258.22</v>
+        <v>44162.44</v>
       </c>
     </row>
     <row r="126">
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>55388.62</v>
+        <v>55268.75</v>
       </c>
     </row>
     <row r="127">
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>247.16</v>
+        <v>246.63</v>
       </c>
     </row>
     <row r="128">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>9795.129999999999</v>
+        <v>9754.059999999999</v>
       </c>
     </row>
     <row r="129">
@@ -8336,7 +8336,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1702.75</v>
+        <v>1695.61</v>
       </c>
     </row>
     <row r="130">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>37105.15</v>
+        <v>36949.6</v>
       </c>
     </row>
     <row r="131">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>22133.55</v>
+        <v>22040.76</v>
       </c>
     </row>
     <row r="132">
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>18610.88</v>
+        <v>18532.86</v>
       </c>
     </row>
     <row r="133">
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>14844.75</v>
+        <v>14782.52</v>
       </c>
     </row>
     <row r="134">
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>44052.04</v>
+        <v>43867.36</v>
       </c>
     </row>
     <row r="135">
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>22071.13</v>
+        <v>21978.6</v>
       </c>
     </row>
     <row r="136">
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>440.1</v>
+        <v>438.25</v>
       </c>
     </row>
     <row r="137">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1810.49</v>
+        <v>1802.9</v>
       </c>
     </row>
     <row r="138">
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>714447.1</v>
+        <v>711451.9300000001</v>
       </c>
     </row>
     <row r="139">
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3336.33</v>
+        <v>3322.35</v>
       </c>
     </row>
     <row r="140">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>6549.05</v>
+        <v>6521.6</v>
       </c>
     </row>
     <row r="141">
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8049.88</v>
+        <v>8016.13</v>
       </c>
     </row>
     <row r="142">
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2239.78</v>
+        <v>2230.39</v>
       </c>
     </row>
     <row r="143">
@@ -9190,7 +9190,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>8997.040000000001</v>
+        <v>8959.32</v>
       </c>
     </row>
     <row r="144">
@@ -9251,7 +9251,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1473.34</v>
+        <v>1467.16</v>
       </c>
     </row>
     <row r="145">
@@ -9312,7 +9312,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5322.23</v>
+        <v>5299.91</v>
       </c>
     </row>
     <row r="146">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>16372.63</v>
+        <v>16303.99</v>
       </c>
     </row>
     <row r="147">
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>63052.08</v>
+        <v>62787.75</v>
       </c>
     </row>
     <row r="148">
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>657.5</v>
+        <v>654.75</v>
       </c>
     </row>
     <row r="149">
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>526546.91</v>
+        <v>524339.47</v>
       </c>
     </row>
     <row r="150">
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>6387.51</v>
+        <v>6360.73</v>
       </c>
     </row>
     <row r="151">
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>61233.64</v>
+        <v>60976.94</v>
       </c>
     </row>
     <row r="152">
@@ -9743,7 +9743,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>23995.41</v>
+        <v>23894.81</v>
       </c>
     </row>
     <row r="153">
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>24370.53</v>
+        <v>24088.48</v>
       </c>
     </row>
     <row r="154">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4366.03</v>
+        <v>4315.51</v>
       </c>
     </row>
     <row r="155">
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1091.51</v>
+        <v>1078.88</v>
       </c>
     </row>
     <row r="156">
@@ -9987,7 +9987,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>10844.25</v>
+        <v>10718.75</v>
       </c>
     </row>
     <row r="157">
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2888.24</v>
+        <v>2854.81</v>
       </c>
     </row>
     <row r="158">
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>31108.52</v>
+        <v>30748.5</v>
       </c>
     </row>
     <row r="159">
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>52886.2</v>
+        <v>52274.14</v>
       </c>
     </row>
     <row r="160">
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3359.66</v>
+        <v>3320.78</v>
       </c>
     </row>
     <row r="161">
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>13615.48</v>
+        <v>13457.91</v>
       </c>
     </row>
     <row r="162">
@@ -10353,7 +10353,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>16368.76</v>
+        <v>16179.32</v>
       </c>
     </row>
     <row r="163">
@@ -10414,7 +10414,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1145.72</v>
+        <v>1132.46</v>
       </c>
     </row>
     <row r="164">
@@ -10475,7 +10475,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>21703.2</v>
+        <v>21452.03</v>
       </c>
     </row>
     <row r="165">
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>5073.53</v>
+        <v>5014.81</v>
       </c>
     </row>
     <row r="166">
@@ -10597,7 +10597,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>21066.34</v>
+        <v>20822.54</v>
       </c>
     </row>
     <row r="167">
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2144.96</v>
+        <v>2120.13</v>
       </c>
     </row>
     <row r="168">
@@ -10719,7 +10719,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1855.56</v>
+        <v>1834.09</v>
       </c>
     </row>
     <row r="169">
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3453.54</v>
+        <v>3413.57</v>
       </c>
     </row>
     <row r="170">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2979.82</v>
+        <v>2945.33</v>
       </c>
     </row>
     <row r="171">
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6786.13</v>
+        <v>6707.59</v>
       </c>
     </row>
     <row r="172">
@@ -10963,7 +10963,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>25110.9</v>
+        <v>24820.29</v>
       </c>
     </row>
     <row r="173">
@@ -11024,7 +11024,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>34928.28</v>
+        <v>34524.05</v>
       </c>
     </row>
     <row r="174">
@@ -11085,7 +11085,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>30081.98</v>
+        <v>29733.84</v>
       </c>
     </row>
     <row r="175">
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2688.67</v>
+        <v>2657.55</v>
       </c>
     </row>
     <row r="176">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>9799.57</v>
+        <v>9686.16</v>
       </c>
     </row>
     <row r="177">
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>36098.09</v>
+        <v>35792.31</v>
       </c>
     </row>
     <row r="178">
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>90173.22</v>
+        <v>89409.38</v>
       </c>
     </row>
     <row r="179">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>9704.25</v>
+        <v>9622.049999999999</v>
       </c>
     </row>
     <row r="180">
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>504.11</v>
+        <v>499.84</v>
       </c>
     </row>
     <row r="181">
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>9955.049999999999</v>
+        <v>9870.719999999999</v>
       </c>
     </row>
     <row r="182">
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9394.620000000001</v>
+        <v>9315.040000000001</v>
       </c>
     </row>
     <row r="183">
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>74.15000000000001</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="184">
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2695.66</v>
+        <v>2672.83</v>
       </c>
     </row>
     <row r="185">
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>38840.25</v>
+        <v>38511.24</v>
       </c>
     </row>
     <row r="186">
@@ -11821,7 +11821,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>54138.84</v>
+        <v>53680.23</v>
       </c>
     </row>
     <row r="187">
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>197.73</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="188">
@@ -11943,7 +11943,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>926.85</v>
+        <v>919</v>
       </c>
     </row>
     <row r="189">
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>62.22</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="190">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>653.27</v>
+        <v>647.73</v>
       </c>
     </row>
     <row r="191">
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18058.19</v>
+        <v>17905.23</v>
       </c>
     </row>
     <row r="192">
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>355.18</v>
+        <v>352.18</v>
       </c>
     </row>
     <row r="193">
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>18610.88</v>
+        <v>18453.23</v>
       </c>
     </row>
     <row r="194">
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>15390.33</v>
+        <v>15259.96</v>
       </c>
     </row>
     <row r="195">
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7460.74</v>
+        <v>7397.54</v>
       </c>
     </row>
     <row r="196">
@@ -12431,7 +12431,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>16372.63</v>
+        <v>16233.94</v>
       </c>
     </row>
     <row r="197">
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>9304.92</v>
+        <v>9226.1</v>
       </c>
     </row>
     <row r="198">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>11622.39</v>
+        <v>11523.93</v>
       </c>
     </row>
     <row r="199">
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>160.65</v>
+        <v>159.29</v>
       </c>
     </row>
     <row r="200">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1357.35</v>
+        <v>1345.85</v>
       </c>
     </row>
     <row r="201">
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>173.01</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="202">
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>86.51000000000001</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="203">
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>3274.53</v>
+        <v>3246.79</v>
       </c>
     </row>
     <row r="204">
@@ -12919,7 +12919,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>22879.94</v>
+        <v>22686.12</v>
       </c>
     </row>
     <row r="205">
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>939.21</v>
+        <v>931.26</v>
       </c>
     </row>
     <row r="206">
@@ -13041,7 +13041,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2689.48</v>
+        <v>2666.7</v>
       </c>
     </row>
     <row r="207">
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>67891.14</v>
+        <v>67316.03999999999</v>
       </c>
     </row>
     <row r="208">
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8112.97</v>
+        <v>8044.24</v>
       </c>
     </row>
     <row r="209">
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1174.02</v>
+        <v>1164.07</v>
       </c>
     </row>
     <row r="210">
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>41.48</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="211">
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>62.22</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="212">
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>33515.24</v>
+        <v>33231.34</v>
       </c>
     </row>
     <row r="213">
@@ -13468,7 +13468,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.9</v>
       </c>
     </row>
     <row r="214">
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>33985.49</v>
+        <v>33958.17</v>
       </c>
     </row>
     <row r="215">
@@ -13590,7 +13590,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1091.51</v>
+        <v>1090.63</v>
       </c>
     </row>
     <row r="216">
@@ -13651,7 +13651,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1844.21</v>
+        <v>1842.73</v>
       </c>
     </row>
     <row r="217">
@@ -13712,7 +13712,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>25017.38</v>
+        <v>24997.27</v>
       </c>
     </row>
     <row r="218">
@@ -13773,7 +13773,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>8766.219999999999</v>
+        <v>8759.18</v>
       </c>
     </row>
     <row r="219">
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1088.78</v>
+        <v>1087.9</v>
       </c>
     </row>
     <row r="220">
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>62032.41</v>
+        <v>61982.55</v>
       </c>
     </row>
     <row r="221">
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>890.67</v>
+        <v>889.95</v>
       </c>
     </row>
     <row r="222">
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>38202.81</v>
+        <v>38172.1</v>
       </c>
     </row>
     <row r="223">
@@ -14082,7 +14082,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>25017.38</v>
+        <v>24997.27</v>
       </c>
     </row>
     <row r="224">
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>627.62</v>
+        <v>627.11</v>
       </c>
     </row>
     <row r="225">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>2171.75</v>
+        <v>2170.01</v>
       </c>
     </row>
     <row r="226">
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>7743.3</v>
+        <v>7737.08</v>
       </c>
     </row>
     <row r="227">
@@ -14326,7 +14326,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>27287.72</v>
+        <v>27265.79</v>
       </c>
     </row>
     <row r="228">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1069.08</v>
+        <v>1068.22</v>
       </c>
     </row>
     <row r="229">
@@ -14448,7 +14448,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>512.22</v>
+        <v>511.81</v>
       </c>
     </row>
     <row r="230">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>16072.47</v>
+        <v>16059.55</v>
       </c>
     </row>
     <row r="231">
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>26405.51</v>
+        <v>26384.28</v>
       </c>
     </row>
     <row r="232">
@@ -14631,7 +14631,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>90.87</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="233">
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7649.82</v>
+        <v>7643.67</v>
       </c>
     </row>
     <row r="234">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>948.79</v>
+        <v>948.03</v>
       </c>
     </row>
     <row r="235">
@@ -14814,7 +14814,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>21491.81</v>
+        <v>21474.53</v>
       </c>
     </row>
     <row r="236">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>42265.4</v>
+        <v>42231.43</v>
       </c>
     </row>
     <row r="237">
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>16191.72</v>
+        <v>16178.7</v>
       </c>
     </row>
     <row r="238">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>5566.69</v>
+        <v>5588.06</v>
       </c>
     </row>
     <row r="239">
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>570.3099999999999</v>
+        <v>572.5</v>
       </c>
     </row>
     <row r="240">
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1200.66</v>
+        <v>1205.27</v>
       </c>
     </row>
     <row r="241">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>12650.59</v>
+        <v>12699.14</v>
       </c>
     </row>
     <row r="242">
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>13441.93</v>
+        <v>13493.52</v>
       </c>
     </row>
     <row r="243">
@@ -15302,7 +15302,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2281.25</v>
+        <v>2290.01</v>
       </c>
     </row>
     <row r="244">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7051.15</v>
+        <v>7078.21</v>
       </c>
     </row>
     <row r="245">
@@ -15424,7 +15424,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3274.53</v>
+        <v>3287.1</v>
       </c>
     </row>
     <row r="246">
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>318.74</v>
+        <v>319.97</v>
       </c>
     </row>
     <row r="247">
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2816.09</v>
+        <v>2826.9</v>
       </c>
     </row>
     <row r="248">
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>11523.52</v>
+        <v>11567.75</v>
       </c>
     </row>
     <row r="249">
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>48633.92</v>
+        <v>48820.59</v>
       </c>
     </row>
     <row r="250">
@@ -15729,7 +15729,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1648.72</v>
+        <v>1656.19</v>
       </c>
     </row>
     <row r="251">
@@ -15790,7 +15790,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>15978.25</v>
+        <v>16050.66</v>
       </c>
     </row>
     <row r="252">
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>3084.6</v>
+        <v>3098.58</v>
       </c>
     </row>
     <row r="253">
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>18610.26</v>
+        <v>18694.59</v>
       </c>
     </row>
     <row r="254">
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3038.79</v>
+        <v>3052.57</v>
       </c>
     </row>
     <row r="255">
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>7815.2</v>
+        <v>7850.62</v>
       </c>
     </row>
     <row r="256">
@@ -16095,7 +16095,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>25293.75</v>
+        <v>25408.37</v>
       </c>
     </row>
     <row r="257">
@@ -16156,7 +16156,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>240.13</v>
+        <v>241.22</v>
       </c>
     </row>
     <row r="258">
@@ -16217,7 +16217,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>9627.110000000001</v>
+        <v>9670.74</v>
       </c>
     </row>
     <row r="259">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>10502.06</v>
+        <v>10549.65</v>
       </c>
     </row>
     <row r="260">
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>18576.95</v>
+        <v>18661.13</v>
       </c>
     </row>
     <row r="261">
@@ -16400,7 +16400,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1629.35</v>
+        <v>1636.74</v>
       </c>
     </row>
     <row r="262">
@@ -16461,7 +16461,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>12023.58</v>
+        <v>12078.06</v>
       </c>
     </row>
     <row r="263">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>3370.03</v>
+        <v>3385.3</v>
       </c>
     </row>
     <row r="264">
@@ -16583,7 +16583,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>514.1</v>
+        <v>516.4299999999999</v>
       </c>
     </row>
     <row r="265">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2586.54</v>
+        <v>2598.27</v>
       </c>
     </row>
     <row r="266">
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1584.87</v>
+        <v>1592.05</v>
       </c>
     </row>
     <row r="267">
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>30793.81</v>
+        <v>30933.36</v>
       </c>
     </row>
     <row r="268">
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>25400.1</v>
+        <v>25515.21</v>
       </c>
     </row>
     <row r="269">
@@ -16892,7 +16892,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>24746.42</v>
+        <v>24858.56</v>
       </c>
     </row>
     <row r="270">
@@ -16953,7 +16953,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>19047.95</v>
+        <v>19134.27</v>
       </c>
     </row>
     <row r="271">
@@ -17014,7 +17014,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>5957.18</v>
+        <v>5984.18</v>
       </c>
     </row>
     <row r="272">
@@ -17075,7 +17075,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>507.55</v>
+        <v>509.85</v>
       </c>
     </row>
     <row r="273">
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>5110.01</v>
+        <v>5133.16</v>
       </c>
     </row>
     <row r="274">
@@ -17197,7 +17197,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>240.13</v>
+        <v>240.77</v>
       </c>
     </row>
     <row r="275">
@@ -17258,7 +17258,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>12018.06</v>
+        <v>12049.93</v>
       </c>
     </row>
     <row r="276">
@@ -17319,7 +17319,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>2514.66</v>
+        <v>2521.33</v>
       </c>
     </row>
     <row r="277">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2305.27</v>
+        <v>2311.38</v>
       </c>
     </row>
     <row r="278">
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3578.46</v>
+        <v>3587.95</v>
       </c>
     </row>
     <row r="279">
@@ -17502,7 +17502,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1542.3</v>
+        <v>1546.39</v>
       </c>
     </row>
     <row r="280">
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>752.8099999999999</v>
+        <v>754.8099999999999</v>
       </c>
     </row>
     <row r="281">
@@ -17624,7 +17624,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>7492.12</v>
+        <v>7511.98</v>
       </c>
     </row>
     <row r="282">
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>24240.39</v>
+        <v>24304.67</v>
       </c>
     </row>
     <row r="283">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>20738.67</v>
+        <v>20793.66</v>
       </c>
     </row>
     <row r="284">
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>327.45</v>
+        <v>328.32</v>
       </c>
     </row>
     <row r="285">
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>18939.07</v>
+        <v>18989.29</v>
       </c>
     </row>
     <row r="286">
@@ -17929,7 +17929,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>163.73</v>
+        <v>164.16</v>
       </c>
     </row>
     <row r="287">
@@ -17990,7 +17990,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>14091.41</v>
+        <v>14128.77</v>
       </c>
     </row>
     <row r="288">
@@ -18055,7 +18055,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>73015.72</v>
+        <v>73209.34</v>
       </c>
     </row>
     <row r="289">
@@ -18116,7 +18116,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>995.46</v>
+        <v>998.1</v>
       </c>
     </row>
     <row r="290">
@@ -18177,7 +18177,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>11538.34</v>
+        <v>11522.15</v>
       </c>
     </row>
     <row r="291">
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>26196.21</v>
+        <v>26159.46</v>
       </c>
     </row>
     <row r="292">
@@ -18299,7 +18299,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3929.43</v>
+        <v>3923.92</v>
       </c>
     </row>
     <row r="293">
@@ -18360,7 +18360,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="294">
@@ -18421,7 +18421,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>20077.1</v>
+        <v>20048.94</v>
       </c>
     </row>
     <row r="295">
@@ -18482,7 +18482,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>4489.92</v>
+        <v>4483.62</v>
       </c>
     </row>
     <row r="296">
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>14190.43</v>
+        <v>14170.53</v>
       </c>
     </row>
     <row r="297">
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>422.55</v>
+        <v>421.96</v>
       </c>
     </row>
     <row r="298">
@@ -18665,7 +18665,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>11916.44</v>
+        <v>11899.72</v>
       </c>
     </row>
     <row r="299">
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>125.52</v>
+        <v>125.35</v>
       </c>
     </row>
     <row r="300">
@@ -18787,7 +18787,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>272.31</v>
+        <v>271.93</v>
       </c>
     </row>
     <row r="301">
@@ -18848,7 +18848,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>5033.17</v>
+        <v>5026.1</v>
       </c>
     </row>
     <row r="302">
@@ -18909,7 +18909,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>52453.27</v>
+        <v>52379.69</v>
       </c>
     </row>
     <row r="303">
@@ -18970,7 +18970,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1810.49</v>
+        <v>1807.95</v>
       </c>
     </row>
     <row r="304">
@@ -19031,7 +19031,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1397.27</v>
+        <v>1395.31</v>
       </c>
     </row>
     <row r="305">
@@ -19092,7 +19092,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>7060.48</v>
+        <v>7050.58</v>
       </c>
     </row>
     <row r="306">
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>771.2</v>
+        <v>770.12</v>
       </c>
     </row>
     <row r="307">
@@ -19214,7 +19214,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1952.82</v>
+        <v>1955.32</v>
       </c>
     </row>
     <row r="308">
@@ -19275,7 +19275,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>38555.26</v>
+        <v>38604.68</v>
       </c>
     </row>
     <row r="309">
@@ -19336,7 +19336,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>349.59</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="310">
@@ -19397,7 +19397,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5052.81</v>
+        <v>5059.29</v>
       </c>
     </row>
     <row r="311">
@@ -19458,7 +19458,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>15877.52</v>
+        <v>15897.88</v>
       </c>
     </row>
     <row r="312">
@@ -19519,7 +19519,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>1077.89</v>
+        <v>1079.27</v>
       </c>
     </row>
     <row r="313">
@@ -19580,7 +19580,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1607.25</v>
+        <v>1609.31</v>
       </c>
     </row>
     <row r="314">
@@ -19641,7 +19641,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>3842.11</v>
+        <v>3847.04</v>
       </c>
     </row>
     <row r="315">
@@ -19702,7 +19702,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3025.66</v>
+        <v>3046.49</v>
       </c>
     </row>
     <row r="316">
@@ -19763,7 +19763,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>545.75</v>
+        <v>549.51</v>
       </c>
     </row>
     <row r="317">
@@ -19824,7 +19824,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>454.35</v>
+        <v>457.48</v>
       </c>
     </row>
     <row r="318">
@@ -19885,7 +19885,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>54575.44</v>
+        <v>54951.09</v>
       </c>
     </row>
     <row r="319">
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>59106.42</v>
+        <v>59513.26</v>
       </c>
     </row>
     <row r="320">
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>51.85</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="321">
@@ -20068,7 +20068,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1637.26</v>
+        <v>1648.53</v>
       </c>
     </row>
     <row r="322">
@@ -20129,7 +20129,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>6723.69</v>
+        <v>6769.97</v>
       </c>
     </row>
     <row r="323">
@@ -20190,7 +20190,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>13098.26</v>
+        <v>13188.42</v>
       </c>
     </row>
     <row r="324">
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2837.92</v>
+        <v>2857.46</v>
       </c>
     </row>
     <row r="325">
@@ -20312,7 +20312,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>10693.29</v>
+        <v>10766.9</v>
       </c>
     </row>
     <row r="326">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>6147.38</v>
+        <v>6189.69</v>
       </c>
     </row>
     <row r="327">
@@ -20434,7 +20434,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>144.08</v>
+        <v>145.07</v>
       </c>
     </row>
     <row r="328">
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>13550.65</v>
+        <v>13643.92</v>
       </c>
     </row>
     <row r="329">
@@ -20556,7 +20556,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>3623.81</v>
+        <v>3648.75</v>
       </c>
     </row>
     <row r="330">
@@ -20617,7 +20617,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>6416.54</v>
+        <v>6460.71</v>
       </c>
     </row>
     <row r="331">
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>873.21</v>
+        <v>879.22</v>
       </c>
     </row>
     <row r="332">
@@ -20739,7 +20739,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>14808.64</v>
+        <v>14910.57</v>
       </c>
     </row>
     <row r="333">
@@ -20800,7 +20800,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>45500.64</v>
+        <v>45813.83</v>
       </c>
     </row>
     <row r="334">
@@ -20861,7 +20861,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>10047.88</v>
+        <v>10117.05</v>
       </c>
     </row>
     <row r="335">
@@ -20922,7 +20922,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>11963.1</v>
+        <v>12065.33</v>
       </c>
     </row>
     <row r="336">
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>126.03</v>
+        <v>127.11</v>
       </c>
     </row>
     <row r="337">
@@ -21044,7 +21044,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>401</v>
+        <v>404.43</v>
       </c>
     </row>
     <row r="338">
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>5141.01</v>
+        <v>5184.94</v>
       </c>
     </row>
     <row r="339">
@@ -21166,7 +21166,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>9940.43</v>
+        <v>10025.38</v>
       </c>
     </row>
     <row r="340">
@@ -21227,7 +21227,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>16809.24</v>
+        <v>16952.88</v>
       </c>
     </row>
     <row r="341">
@@ -21288,7 +21288,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>4366.03</v>
+        <v>4403.35</v>
       </c>
     </row>
     <row r="342">
@@ -21349,7 +21349,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>35245.53</v>
+        <v>35546.73</v>
       </c>
     </row>
     <row r="343">
@@ -21410,7 +21410,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>436.6</v>
+        <v>440.33</v>
       </c>
     </row>
     <row r="344">
@@ -21471,7 +21471,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>7531.41</v>
+        <v>7595.77</v>
       </c>
     </row>
     <row r="345">
@@ -21532,7 +21532,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>27287.72</v>
+        <v>27520.91</v>
       </c>
     </row>
     <row r="346">
@@ -21597,7 +21597,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>252913.25</v>
+        <v>255074.6</v>
       </c>
     </row>
     <row r="347">
@@ -21658,7 +21658,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>17249.18</v>
+        <v>17396.59</v>
       </c>
     </row>
     <row r="348">
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>65490.7</v>
+        <v>66050.37</v>
       </c>
     </row>
     <row r="349">
@@ -21780,7 +21780,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>13098.11</v>
+        <v>13210.04</v>
       </c>
     </row>
     <row r="350">
@@ -21841,7 +21841,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>2443.01</v>
+        <v>2463.89</v>
       </c>
     </row>
     <row r="351">
@@ -21902,7 +21902,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>13735.55</v>
+        <v>13882.88</v>
       </c>
     </row>
     <row r="352">
@@ -21963,7 +21963,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>2694.33</v>
+        <v>2723.23</v>
       </c>
     </row>
     <row r="353">
@@ -22028,7 +22028,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>76382.10000000001</v>
+        <v>77201.42</v>
       </c>
     </row>
     <row r="354">
@@ -22089,7 +22089,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>8186.32</v>
+        <v>8274.129999999999</v>
       </c>
     </row>
     <row r="355">
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2183.02</v>
+        <v>2206.43</v>
       </c>
     </row>
     <row r="356">
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>10369.33</v>
+        <v>10480.56</v>
       </c>
     </row>
     <row r="357">
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>13796.65</v>
+        <v>13966.21</v>
       </c>
     </row>
     <row r="358">
@@ -22333,7 +22333,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>18756.93</v>
+        <v>18987.46</v>
       </c>
     </row>
     <row r="359">
@@ -22394,7 +22394,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>17624.24</v>
+        <v>17840.84</v>
       </c>
     </row>
     <row r="360">
@@ -22455,7 +22455,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>54575.44</v>
+        <v>55246.18</v>
       </c>
     </row>
     <row r="361">
@@ -22516,7 +22516,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>55116.67</v>
+        <v>55794.06</v>
       </c>
     </row>
     <row r="362">
@@ -22577,7 +22577,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>30562.25</v>
+        <v>30937.86</v>
       </c>
     </row>
     <row r="363">
@@ -22638,7 +22638,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2507.84</v>
+        <v>2538.66</v>
       </c>
     </row>
     <row r="364">
@@ -22699,7 +22699,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>12063.72</v>
+        <v>12211.98</v>
       </c>
     </row>
     <row r="365">
@@ -22760,7 +22760,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>12812.43</v>
+        <v>12969.89</v>
       </c>
     </row>
     <row r="366">
@@ -22821,7 +22821,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>16372.63</v>
+        <v>16573.85</v>
       </c>
     </row>
     <row r="367">
@@ -22882,7 +22882,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>103.69</v>
+        <v>104.97</v>
       </c>
     </row>
     <row r="368">
@@ -22943,7 +22943,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>15554.73</v>
+        <v>15745.89</v>
       </c>
     </row>
     <row r="369">
@@ -23004,7 +23004,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>36019.79</v>
+        <v>36462.48</v>
       </c>
     </row>
     <row r="370">
@@ -23065,7 +23065,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>3601.98</v>
+        <v>3648.26</v>
       </c>
     </row>
     <row r="371">
@@ -23126,7 +23126,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>446.4</v>
+        <v>452.14</v>
       </c>
     </row>
     <row r="372">
@@ -23187,7 +23187,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>27736.31</v>
+        <v>28092.71</v>
       </c>
     </row>
     <row r="373">
@@ -23248,7 +23248,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>13622.03</v>
+        <v>13797.07</v>
       </c>
     </row>
     <row r="374">
@@ -23309,7 +23309,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>34604.27</v>
+        <v>35048.92</v>
       </c>
     </row>
     <row r="375">
@@ -23370,7 +23370,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1344.74</v>
+        <v>1362.02</v>
       </c>
     </row>
     <row r="376">
@@ -23431,7 +23431,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>163.48</v>
+        <v>165.58</v>
       </c>
     </row>
     <row r="377">
@@ -23492,7 +23492,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>49782.73</v>
+        <v>50422.42</v>
       </c>
     </row>
     <row r="378">
@@ -23557,7 +23557,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>62336.51</v>
+        <v>63137.51</v>
       </c>
     </row>
     <row r="379">
@@ -23618,7 +23618,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>12443.2</v>
+        <v>12603.09</v>
       </c>
     </row>
     <row r="380">
@@ -23679,7 +23679,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>57031.34</v>
+        <v>57764.17</v>
       </c>
     </row>
     <row r="381">
@@ -23740,7 +23740,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4633.54</v>
+        <v>4693.08</v>
       </c>
     </row>
     <row r="382">
@@ -23801,7 +23801,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>362.93</v>
+        <v>367.59</v>
       </c>
     </row>
     <row r="383">
@@ -23862,7 +23862,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>3629.27</v>
+        <v>3675.9</v>
       </c>
     </row>
     <row r="384">
@@ -23923,7 +23923,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>23027.7</v>
+        <v>23323.6</v>
       </c>
     </row>
     <row r="385">
@@ -23984,7 +23984,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>1163.96</v>
+        <v>1178.91</v>
       </c>
     </row>
     <row r="386">
@@ -24045,7 +24045,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>17969.02</v>
+        <v>18199.91</v>
       </c>
     </row>
     <row r="387">
@@ -24106,7 +24106,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>10915.09</v>
+        <v>11055.34</v>
       </c>
     </row>
     <row r="388">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>545.75</v>
+        <v>552.77</v>
       </c>
     </row>
     <row r="389">
@@ -24228,7 +24228,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>61634.23</v>
+        <v>61971.29</v>
       </c>
     </row>
     <row r="390">
@@ -24289,7 +24289,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>12961.67</v>
+        <v>13032.55</v>
       </c>
     </row>
     <row r="391">
@@ -24350,7 +24350,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>18088.37</v>
+        <v>18187.29</v>
       </c>
     </row>
     <row r="392">
@@ -24411,7 +24411,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1503.16</v>
+        <v>1511.38</v>
       </c>
     </row>
     <row r="393">
@@ -24472,7 +24472,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>32898.56</v>
+        <v>33078.48</v>
       </c>
     </row>
     <row r="394">
@@ -24533,7 +24533,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>36019.79</v>
+        <v>36216.77</v>
       </c>
     </row>
     <row r="395">
@@ -24594,7 +24594,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>4536.31</v>
+        <v>4561.12</v>
       </c>
     </row>
     <row r="396">
@@ -24655,7 +24655,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>62216</v>
+        <v>62556.25</v>
       </c>
     </row>
     <row r="397">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>47486.36</v>
+        <v>47746.05</v>
       </c>
     </row>
     <row r="398">
@@ -24777,7 +24777,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>936.52</v>
+        <v>941.64</v>
       </c>
     </row>
     <row r="399">
@@ -24838,7 +24838,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>22921.69</v>
+        <v>23047.04</v>
       </c>
     </row>
     <row r="400">
@@ -24899,7 +24899,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>32296.33</v>
+        <v>32472.95</v>
       </c>
     </row>
     <row r="401">
@@ -24960,7 +24960,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>40813.7</v>
+        <v>41036.9</v>
       </c>
     </row>
     <row r="402">
@@ -25021,7 +25021,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>21775.6</v>
+        <v>21894.69</v>
       </c>
     </row>
     <row r="403">
@@ -25082,7 +25082,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>30848.77</v>
+        <v>31017.47</v>
       </c>
     </row>
     <row r="404">
@@ -25143,7 +25143,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>25440.19</v>
+        <v>25579.31</v>
       </c>
     </row>
     <row r="405">
@@ -25204,7 +25204,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>69993</v>
+        <v>70375.78</v>
       </c>
     </row>
     <row r="406">
@@ -25265,7 +25265,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>134801.34</v>
+        <v>135538.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11065,7 +11065,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16319,7 +16319,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16624,7 +16624,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18046,7 +18046,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18401,7 +18401,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20597,7 +20597,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -22557,7 +22557,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -24635,7 +24635,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24818,7 +24818,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA PRIMERA ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
+          <t>DIRECCION DE COMPRAS Y CONTRATACION PUBLICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>INNOVA CHILE</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comité para el Fomento de la Economía Asociativa </t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Comité de Desarrollo de la Industria de Hidrógeno</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Comité de Desarrollo y Fomento Indígena</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>3a Briagada Acorazada "La Concepción"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Com.Desarrollo Productivo Regional de Los Ríos</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11857,7 +11857,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12833,7 +12833,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13692,7 +13692,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Comité de Des Productivo Regional Antofagasta</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14550,7 +14550,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15216,7 +15216,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO FRONTERAS OS3</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SII Oficina de Bienestar</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16928,7 +16928,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO FRONTERAS OS3</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Superintendencia de Servicios Sanitarios</t>
+          <t>SUPERINTENDENCIA DE SERVICIOS SANITARIOS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Dirección Servicio Metropolitano Oriente</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Departamento Provincial de Educación Copiapo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21141,7 +21141,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Servicio Salud Antof</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21263,7 +21263,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -21385,7 +21385,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22308,7 +22308,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano San Felipe</t>
+          <t>CONSULTORIO GENERAL URBANO SAN FELIPE</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -24081,7 +24081,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Dirección Servicio Metropolitano Oriente</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24996,7 +24996,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7101,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7227,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7288,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7349,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7475,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7536,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7597,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7658,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7719,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7780,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7841,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7902,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7963,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8024,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8085,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8146,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8207,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8268,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8329,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8390,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8451,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8512,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8573,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8634,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8695,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8756,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8817,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8878,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8939,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9000,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9061,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9122,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9183,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9244,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9305,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9366,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9492,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9553,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9614,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9675,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9736,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9797,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9858,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9919,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9980,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10041,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10102,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10163,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10224,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10285,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10346,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10407,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10468,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10529,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10590,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10651,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10712,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10773,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10834,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10895,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10956,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11017,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11078,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11139,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11200,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11261,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11322,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11383,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11444,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11505,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11566,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11627,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11688,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11749,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11875,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11936,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11997,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12058,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12119,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12180,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12241,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12302,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12363,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12424,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12485,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12546,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12607,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12668,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12729,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12790,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12851,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12912,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12973,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13034,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13095,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13156,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13217,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13278,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13339,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13400,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13461,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13522,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13583,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13644,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13705,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13766,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13827,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13953,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14014,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14075,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14136,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14197,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14258,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14319,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14380,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14441,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14502,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14563,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14624,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14685,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14746,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14807,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14868,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14929,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14990,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15051,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15112,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15173,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15234,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15295,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15356,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15417,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15478,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15539,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15600,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15661,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15722,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15783,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15844,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15905,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15966,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16027,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16088,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16149,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16210,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16271,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16332,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16393,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16454,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16515,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16576,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16637,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16698,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16759,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16885,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16946,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17007,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17068,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17129,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17190,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17251,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17312,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17373,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17434,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17495,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17556,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17617,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17678,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17739,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17800,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17861,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17922,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17983,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18109,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18170,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18231,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18292,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18353,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18414,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18475,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18536,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18597,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18658,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18719,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18780,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18841,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18902,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18963,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19024,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19085,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19146,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19207,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19268,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19329,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19390,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19451,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19512,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19573,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19634,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19695,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19756,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19817,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19878,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19939,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20000,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20061,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20122,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20183,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20244,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20305,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20366,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20427,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20488,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20549,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20610,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20671,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20732,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20793,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20854,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20915,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20976,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21037,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21098,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21159,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21220,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21281,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21342,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21403,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21464,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21525,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21651,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21712,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21773,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21834,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21895,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21956,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22082,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22143,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22204,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22265,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22326,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22387,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22448,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22509,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22570,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22631,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22692,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22753,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22814,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22875,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22936,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22997,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23058,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23119,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23180,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23241,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23302,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23363,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23424,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23485,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23611,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23672,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23733,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23794,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23855,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23916,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23977,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24038,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24099,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24160,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24221,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24282,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24343,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24404,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24465,7 +25977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24526,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24587,7 +26107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24648,7 +26172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24709,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24770,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24831,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24892,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24953,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25014,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25075,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25136,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25197,7 +26757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25258,7 +26822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
